--- a/public/excel/product/Giá đặc tròn C45 ( chế tạo).xlsx
+++ b/public/excel/product/Giá đặc tròn C45 ( chế tạo).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="58">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép tròn chế tạo S45C: F14 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép tròn chế tạo S45C: F16 x 6m</t>
@@ -424,7 +430,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.28"/>
@@ -461,10 +467,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>6</v>
@@ -485,15 +494,18 @@
         <v>104.048</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>6</v>
@@ -514,15 +526,18 @@
         <v>135.235</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>6</v>
@@ -543,15 +558,18 @@
         <v>168.354</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>6</v>
@@ -572,15 +590,18 @@
         <v>209.752</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>6</v>
@@ -601,15 +622,18 @@
         <v>331.188</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>6</v>
@@ -630,15 +654,18 @@
         <v>465.043</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>6</v>
@@ -659,15 +686,18 @@
         <v>531.281</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>6</v>
@@ -688,15 +718,18 @@
         <v>641.677</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>6</v>
@@ -717,15 +750,18 @@
         <v>827.97</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>6</v>
@@ -746,15 +782,18 @@
         <v>855.569</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>6</v>
@@ -772,18 +811,21 @@
         <v>13.8</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>6</v>
@@ -795,24 +837,27 @@
         <v>12.545</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>6</v>
@@ -824,24 +869,27 @@
         <v>12.545</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>6</v>
@@ -853,24 +901,27 @@
         <v>12.545</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>6</v>
@@ -882,24 +933,27 @@
         <v>12.545</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>6</v>
@@ -911,24 +965,27 @@
         <v>12.545</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>6</v>
@@ -940,24 +997,27 @@
         <v>12.545</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>6</v>
@@ -969,24 +1029,27 @@
         <v>12.545</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>6</v>
@@ -998,24 +1061,27 @@
         <v>12.545</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>6</v>
@@ -1027,24 +1093,27 @@
         <v>12.545</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>6</v>
@@ -1056,24 +1125,27 @@
         <v>12.545</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>6</v>
@@ -1085,19 +1157,22 @@
         <v>12.545</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
